--- a/web/templates/Project5/David_version/07_final_PCBmass_SPME.xlsx
+++ b/web/templates/Project5/David_version/07_final_PCBmass_SPME.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixi\Documents\DataHarmonizerDevelop\web\templates\Project5\David_version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6907039E-BD08-487E-90FA-6DA113F3DAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603C7C59-C58E-4541-B614-AE26F013960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>LCPCB</t>
-  </si>
-  <si>
-    <t>PCB_141</t>
   </si>
   <si>
     <t>biochar_percentage</t>
@@ -627,6 +624,9 @@
   <si>
     <t>PCB209</t>
   </si>
+  <si>
+    <t>PCB141</t>
+  </si>
 </sst>
 </file>
 
@@ -31086,534 +31086,534 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>26</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>35</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>37</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>38</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>39</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>40</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>41</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>42</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>43</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>44</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>45</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>46</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>47</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>48</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>49</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>50</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>51</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>52</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>53</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>54</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>55</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>56</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>57</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>58</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>59</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>60</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>61</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>62</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>63</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>64</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>65</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>66</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>67</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>68</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>69</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>70</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>71</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>72</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>73</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>74</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>75</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>76</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>77</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>78</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>79</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>80</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>81</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>82</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>83</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>84</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>85</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>86</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>87</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>88</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>89</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>90</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>91</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>92</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>93</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>94</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>95</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>96</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>97</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>98</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>99</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>100</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>101</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>102</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>103</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>104</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>105</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>106</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>107</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>108</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>109</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>110</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>111</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>112</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>113</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>114</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>115</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>116</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>117</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>118</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DJ1" t="s">
         <v>119</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DK1" t="s">
         <v>120</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DL1" t="s">
         <v>121</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DM1" t="s">
         <v>122</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DN1" t="s">
         <v>123</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DO1" t="s">
         <v>124</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DP1" t="s">
         <v>125</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DQ1" t="s">
         <v>126</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DR1" t="s">
         <v>127</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DS1" t="s">
         <v>128</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="DT1" t="s">
+        <v>187</v>
+      </c>
+      <c r="DU1" t="s">
         <v>129</v>
       </c>
-      <c r="DT1" t="s">
-        <v>9</v>
-      </c>
-      <c r="DU1" t="s">
+      <c r="DV1" t="s">
         <v>130</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="DW1" t="s">
         <v>131</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="DX1" t="s">
         <v>132</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DY1" t="s">
         <v>133</v>
       </c>
-      <c r="DY1" t="s">
+      <c r="DZ1" t="s">
         <v>134</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EA1" t="s">
         <v>135</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EB1" t="s">
         <v>136</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="EC1" t="s">
         <v>137</v>
       </c>
-      <c r="EC1" t="s">
+      <c r="ED1" t="s">
         <v>138</v>
       </c>
-      <c r="ED1" t="s">
+      <c r="EE1" t="s">
         <v>139</v>
       </c>
-      <c r="EE1" t="s">
+      <c r="EF1" t="s">
         <v>140</v>
       </c>
-      <c r="EF1" t="s">
+      <c r="EG1" t="s">
         <v>141</v>
       </c>
-      <c r="EG1" t="s">
+      <c r="EH1" t="s">
         <v>142</v>
       </c>
-      <c r="EH1" t="s">
+      <c r="EI1" t="s">
         <v>143</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="EJ1" t="s">
         <v>144</v>
       </c>
-      <c r="EJ1" t="s">
+      <c r="EK1" t="s">
         <v>145</v>
       </c>
-      <c r="EK1" t="s">
+      <c r="EL1" t="s">
         <v>146</v>
       </c>
-      <c r="EL1" t="s">
+      <c r="EM1" t="s">
         <v>147</v>
       </c>
-      <c r="EM1" t="s">
+      <c r="EN1" t="s">
         <v>148</v>
       </c>
-      <c r="EN1" t="s">
+      <c r="EO1" t="s">
         <v>149</v>
       </c>
-      <c r="EO1" t="s">
+      <c r="EP1" t="s">
         <v>150</v>
       </c>
-      <c r="EP1" t="s">
+      <c r="EQ1" t="s">
         <v>151</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="ER1" t="s">
         <v>152</v>
       </c>
-      <c r="ER1" t="s">
+      <c r="ES1" t="s">
         <v>153</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="ET1" t="s">
         <v>154</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EU1" t="s">
         <v>155</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EV1" t="s">
         <v>156</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EW1" t="s">
         <v>157</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="EX1" t="s">
         <v>158</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="EY1" t="s">
         <v>159</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="EZ1" t="s">
         <v>160</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FA1" t="s">
         <v>161</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FB1" t="s">
         <v>162</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FC1" t="s">
         <v>163</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FD1" t="s">
         <v>164</v>
       </c>
-      <c r="FD1" t="s">
+      <c r="FE1" t="s">
         <v>165</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FF1" t="s">
         <v>166</v>
       </c>
-      <c r="FF1" t="s">
+      <c r="FG1" t="s">
         <v>167</v>
       </c>
-      <c r="FG1" t="s">
+      <c r="FH1" t="s">
         <v>168</v>
       </c>
-      <c r="FH1" t="s">
+      <c r="FI1" t="s">
         <v>169</v>
       </c>
-      <c r="FI1" t="s">
+      <c r="FJ1" t="s">
         <v>170</v>
       </c>
-      <c r="FJ1" t="s">
+      <c r="FK1" t="s">
         <v>171</v>
       </c>
-      <c r="FK1" t="s">
+      <c r="FL1" t="s">
         <v>172</v>
       </c>
-      <c r="FL1" t="s">
+      <c r="FM1" t="s">
         <v>173</v>
       </c>
-      <c r="FM1" t="s">
+      <c r="FN1" t="s">
         <v>174</v>
       </c>
-      <c r="FN1" t="s">
+      <c r="FO1" t="s">
         <v>175</v>
       </c>
-      <c r="FO1" t="s">
+      <c r="FP1" t="s">
         <v>176</v>
       </c>
-      <c r="FP1" t="s">
+      <c r="FQ1" t="s">
         <v>177</v>
       </c>
-      <c r="FQ1" t="s">
+      <c r="FR1" t="s">
         <v>178</v>
       </c>
-      <c r="FR1" t="s">
+      <c r="FS1" t="s">
         <v>179</v>
       </c>
-      <c r="FS1" t="s">
+      <c r="FT1" t="s">
         <v>180</v>
       </c>
-      <c r="FT1" t="s">
+      <c r="FU1" t="s">
         <v>181</v>
       </c>
-      <c r="FU1" t="s">
+      <c r="FV1" t="s">
         <v>182</v>
       </c>
-      <c r="FV1" t="s">
+      <c r="FW1" t="s">
         <v>183</v>
       </c>
-      <c r="FW1" t="s">
+      <c r="FX1" t="s">
         <v>184</v>
       </c>
-      <c r="FX1" t="s">
+      <c r="FY1" t="s">
         <v>185</v>
       </c>
-      <c r="FY1" t="s">
+      <c r="FZ1" t="s">
         <v>186</v>
-      </c>
-      <c r="FZ1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -31622,7 +31622,7 @@
         <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -32158,13 +32158,13 @@
     </row>
     <row r="3" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -32173,7 +32173,7 @@
         <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -32706,13 +32706,13 @@
     </row>
     <row r="4" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -32721,7 +32721,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -33254,13 +33254,13 @@
     </row>
     <row r="5" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -33269,7 +33269,7 @@
         <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -33802,13 +33802,13 @@
     </row>
     <row r="6" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -33817,7 +33817,7 @@
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -34350,13 +34350,13 @@
     </row>
     <row r="7" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -34365,7 +34365,7 @@
         <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -34898,13 +34898,13 @@
     </row>
     <row r="8" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -34913,7 +34913,7 @@
         <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -35446,13 +35446,13 @@
     </row>
     <row r="9" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -35461,7 +35461,7 @@
         <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -35994,13 +35994,13 @@
     </row>
     <row r="10" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -36009,7 +36009,7 @@
         <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -36542,13 +36542,13 @@
     </row>
     <row r="11" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -36557,7 +36557,7 @@
         <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -37090,13 +37090,13 @@
     </row>
     <row r="12" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -37105,7 +37105,7 @@
         <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -37638,13 +37638,13 @@
     </row>
     <row r="13" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -37653,7 +37653,7 @@
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -38186,13 +38186,13 @@
     </row>
     <row r="14" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>1.5</v>
@@ -38201,7 +38201,7 @@
         <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -38734,13 +38734,13 @@
     </row>
     <row r="15" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15">
         <v>1.5</v>
@@ -38749,7 +38749,7 @@
         <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -39282,13 +39282,13 @@
     </row>
     <row r="16" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>1.5</v>
@@ -39297,7 +39297,7 @@
         <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -39830,13 +39830,13 @@
     </row>
     <row r="17" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>1.5</v>
@@ -39845,7 +39845,7 @@
         <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -40378,13 +40378,13 @@
     </row>
     <row r="18" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>1.5</v>
@@ -40393,7 +40393,7 @@
         <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -40926,13 +40926,13 @@
     </row>
     <row r="19" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>1.5</v>
@@ -40941,7 +40941,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -41474,13 +41474,13 @@
     </row>
     <row r="20" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -42022,13 +42022,13 @@
     </row>
     <row r="21" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -42037,7 +42037,7 @@
         <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -42570,13 +42570,13 @@
     </row>
     <row r="22" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
         <v>13</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -42585,7 +42585,7 @@
         <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -43118,13 +43118,13 @@
     </row>
     <row r="23" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
         <v>13</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -43133,7 +43133,7 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -43669,13 +43669,13 @@
     </row>
     <row r="24" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
         <v>13</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -43684,7 +43684,7 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -44217,13 +44217,13 @@
     </row>
     <row r="25" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
         <v>13</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -44232,7 +44232,7 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>3</v>
@@ -44765,13 +44765,13 @@
     </row>
     <row r="26" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
         <v>13</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>14</v>
-      </c>
-      <c r="C26" t="s">
-        <v>15</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -44780,7 +44780,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -45313,13 +45313,13 @@
     </row>
     <row r="27" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
         <v>13</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>14</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -45328,7 +45328,7 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -45861,13 +45861,13 @@
     </row>
     <row r="28" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>14</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -45876,7 +45876,7 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -46409,13 +46409,13 @@
     </row>
     <row r="29" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
         <v>13</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -46424,7 +46424,7 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -46957,13 +46957,13 @@
     </row>
     <row r="30" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
         <v>13</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>14</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -46972,7 +46972,7 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -47505,13 +47505,13 @@
     </row>
     <row r="31" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
         <v>13</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -47520,7 +47520,7 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -48053,13 +48053,13 @@
     </row>
     <row r="32" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
         <v>13</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>14</v>
-      </c>
-      <c r="C32" t="s">
-        <v>15</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -48068,7 +48068,7 @@
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -48601,13 +48601,13 @@
     </row>
     <row r="33" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
         <v>13</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>14</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -48616,7 +48616,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -49149,13 +49149,13 @@
     </row>
     <row r="34" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
         <v>13</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>15</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -49164,7 +49164,7 @@
         <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -49697,13 +49697,13 @@
     </row>
     <row r="35" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
         <v>13</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -49712,7 +49712,7 @@
         <v>25</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -50245,13 +50245,13 @@
     </row>
     <row r="36" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
         <v>13</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -50260,7 +50260,7 @@
         <v>25</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -50793,13 +50793,13 @@
     </row>
     <row r="37" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
         <v>13</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>15</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -50808,7 +50808,7 @@
         <v>25</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -51341,13 +51341,13 @@
     </row>
     <row r="38" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>15</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -51356,7 +51356,7 @@
         <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -51364,13 +51364,13 @@
     </row>
     <row r="39" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
         <v>13</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>15</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -51379,7 +51379,7 @@
         <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -51915,13 +51915,13 @@
     </row>
     <row r="40" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
         <v>13</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -51930,7 +51930,7 @@
         <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -52463,13 +52463,13 @@
     </row>
     <row r="41" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
         <v>13</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>14</v>
-      </c>
-      <c r="C41" t="s">
-        <v>15</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -52478,7 +52478,7 @@
         <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -53011,13 +53011,13 @@
     </row>
     <row r="42" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
         <v>13</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>14</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -53026,7 +53026,7 @@
         <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -53559,13 +53559,13 @@
     </row>
     <row r="43" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
         <v>13</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>14</v>
-      </c>
-      <c r="C43" t="s">
-        <v>15</v>
       </c>
       <c r="D43">
         <v>5</v>
@@ -53574,7 +53574,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -54107,13 +54107,13 @@
     </row>
     <row r="44" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>14</v>
-      </c>
-      <c r="C44" t="s">
-        <v>15</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -54122,7 +54122,7 @@
         <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -54655,13 +54655,13 @@
     </row>
     <row r="45" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
         <v>13</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>14</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
       </c>
       <c r="D45">
         <v>5</v>
@@ -54670,7 +54670,7 @@
         <v>60</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -55203,13 +55203,13 @@
     </row>
     <row r="46" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>14</v>
-      </c>
-      <c r="C46" t="s">
-        <v>15</v>
       </c>
       <c r="D46">
         <v>5</v>
@@ -55218,7 +55218,7 @@
         <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>3</v>
@@ -55751,13 +55751,13 @@
     </row>
     <row r="47" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
         <v>13</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="C47" t="s">
-        <v>15</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -55766,7 +55766,7 @@
         <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -56299,13 +56299,13 @@
     </row>
     <row r="48" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
         <v>13</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>15</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -56314,7 +56314,7 @@
         <v>60</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -56847,13 +56847,13 @@
     </row>
     <row r="49" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
         <v>13</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>15</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -56862,7 +56862,7 @@
         <v>60</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -57395,13 +57395,13 @@
     </row>
     <row r="50" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
         <v>13</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>14</v>
-      </c>
-      <c r="C50" t="s">
-        <v>15</v>
       </c>
       <c r="D50">
         <v>5</v>
@@ -57410,7 +57410,7 @@
         <v>120</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -57943,13 +57943,13 @@
     </row>
     <row r="51" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
         <v>13</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>14</v>
-      </c>
-      <c r="C51" t="s">
-        <v>15</v>
       </c>
       <c r="D51">
         <v>5</v>
@@ -57958,7 +57958,7 @@
         <v>120</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -58491,13 +58491,13 @@
     </row>
     <row r="52" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
         <v>13</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>14</v>
-      </c>
-      <c r="C52" t="s">
-        <v>15</v>
       </c>
       <c r="D52">
         <v>5</v>
@@ -58506,7 +58506,7 @@
         <v>120</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -59039,13 +59039,13 @@
     </row>
     <row r="53" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
         <v>13</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>14</v>
-      </c>
-      <c r="C53" t="s">
-        <v>15</v>
       </c>
       <c r="D53">
         <v>5</v>
@@ -59054,7 +59054,7 @@
         <v>120</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -59587,13 +59587,13 @@
     </row>
     <row r="54" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
         <v>13</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>14</v>
-      </c>
-      <c r="C54" t="s">
-        <v>15</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -59602,7 +59602,7 @@
         <v>120</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -60135,13 +60135,13 @@
     </row>
     <row r="55" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
         <v>13</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>14</v>
-      </c>
-      <c r="C55" t="s">
-        <v>15</v>
       </c>
       <c r="D55">
         <v>5</v>
@@ -60150,7 +60150,7 @@
         <v>120</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -60683,13 +60683,13 @@
     </row>
     <row r="56" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
         <v>13</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="C56" t="s">
-        <v>15</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -60698,7 +60698,7 @@
         <v>120</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -61231,13 +61231,13 @@
     </row>
     <row r="57" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
         <v>13</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>14</v>
-      </c>
-      <c r="C57" t="s">
-        <v>15</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -61246,7 +61246,7 @@
         <v>120</v>
       </c>
       <c r="F57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -61779,13 +61779,13 @@
     </row>
     <row r="58" spans="1:182" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
         <v>13</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>14</v>
-      </c>
-      <c r="C58" t="s">
-        <v>15</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -61794,7 +61794,7 @@
         <v>120</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G58">
         <v>3</v>
